--- a/backend/PDF_DOC/DGFT/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/DGFT/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24841309-700C-40EB-AE00-56C837172B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F5492C-2FC9-4DB5-92B1-914F93CA5375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="903">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2735,6 +2735,12 @@
   </si>
   <si>
     <t>Request for comments on alignment of Schedule-II (Export Policy) of ITC (HS), 2022 consequent to amendments introduced under the Finance Act, 2026 – regarding.</t>
+  </si>
+  <si>
+    <t>NOTIFICATION- 21/2026-27</t>
+  </si>
+  <si>
+    <t>Amendment to Notification No. 35/2025-26 for extension of timelines under Component II of Resilience &amp; Logistics Intervention for Export Facilitation (RELIEF) Intervention - reg</t>
   </si>
 </sst>
 </file>
@@ -5946,7 +5952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
@@ -5986,16 +5992,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="62" t="s">
-        <v>887</v>
+        <v>901</v>
       </c>
       <c r="C5" s="63" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D5" s="62" t="s">
-        <v>888</v>
+        <v>902</v>
       </c>
       <c r="E5" s="64">
-        <v>46175</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6003,13 +6009,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="C6" s="63" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E6" s="64">
         <v>46175</v>
@@ -6020,13 +6026,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>891</v>
-      </c>
-      <c r="C7" s="63">
-        <v>2026</v>
+        <v>889</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>819</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E7" s="64">
         <v>46175</v>
@@ -6036,17 +6042,17 @@
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>874</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>819</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>875</v>
-      </c>
-      <c r="E8" s="49">
-        <v>46158</v>
+      <c r="B8" s="62" t="s">
+        <v>891</v>
+      </c>
+      <c r="C8" s="63">
+        <v>2026</v>
+      </c>
+      <c r="D8" s="62" t="s">
+        <v>892</v>
+      </c>
+      <c r="E8" s="64">
+        <v>46175</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6054,16 +6060,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E9" s="49">
-        <v>46155</v>
+        <v>46158</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6071,16 +6077,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>855</v>
-      </c>
-      <c r="E10" s="40">
-        <v>46142</v>
+        <v>873</v>
+      </c>
+      <c r="E10" s="49">
+        <v>46155</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6088,13 +6094,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>856</v>
-      </c>
-      <c r="C11" s="35">
-        <v>2026</v>
+        <v>854</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E11" s="40">
         <v>46142</v>
@@ -6105,16 +6111,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>858</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>819</v>
+        <v>856</v>
+      </c>
+      <c r="C12" s="35">
+        <v>2026</v>
       </c>
       <c r="D12" s="34" t="s">
-        <v>764</v>
+        <v>857</v>
       </c>
       <c r="E12" s="40">
-        <v>46139</v>
+        <v>46142</v>
       </c>
     </row>
     <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6122,30 +6128,30 @@
         <v>9</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D13" s="34" t="s">
-        <v>845</v>
+        <v>764</v>
       </c>
       <c r="E13" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C14" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D14" s="34" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E14" s="40">
         <v>46129</v>
@@ -6155,17 +6161,17 @@
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>831</v>
-      </c>
-      <c r="C15" s="24" t="s">
+      <c r="B15" s="34" t="s">
+        <v>842</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>832</v>
-      </c>
-      <c r="E15" s="41">
-        <v>46122</v>
+      <c r="D15" s="34" t="s">
+        <v>843</v>
+      </c>
+      <c r="E15" s="40">
+        <v>46129</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -6173,13 +6179,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E16" s="41">
         <v>46122</v>
@@ -6190,13 +6196,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C17" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>43</v>
+        <v>834</v>
       </c>
       <c r="E17" s="41">
         <v>46122</v>
@@ -6207,33 +6213,33 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>829</v>
+        <v>835</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>819</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>830</v>
+        <v>43</v>
       </c>
       <c r="E18" s="41">
-        <v>46121</v>
+        <v>46122</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" t="s">
-        <v>823</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B19" s="21" t="s">
+        <v>829</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>819</v>
       </c>
-      <c r="D19" t="s">
-        <v>824</v>
-      </c>
-      <c r="E19" s="38">
-        <v>46119</v>
+      <c r="D19" s="21" t="s">
+        <v>830</v>
+      </c>
+      <c r="E19" s="41">
+        <v>46121</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -6241,16 +6247,16 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>819</v>
       </c>
       <c r="D20" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E20" s="38">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -6258,16 +6264,16 @@
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>819</v>
       </c>
       <c r="D21" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E21" s="38">
-        <v>46114</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -6275,16 +6281,16 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>816</v>
-      </c>
-      <c r="C22" s="8">
-        <v>2026</v>
+        <v>827</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>819</v>
       </c>
       <c r="D22" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="E22" s="38">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -6292,13 +6298,13 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>818</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>819</v>
+        <v>816</v>
+      </c>
+      <c r="C23" s="8">
+        <v>2026</v>
       </c>
       <c r="D23" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="E23" s="38">
         <v>46113</v>
@@ -6308,16 +6314,16 @@
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="21" t="s">
-        <v>816</v>
-      </c>
-      <c r="C24" s="24">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>817</v>
-      </c>
-      <c r="E24" s="41">
+      <c r="B24" t="s">
+        <v>818</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D24" t="s">
+        <v>820</v>
+      </c>
+      <c r="E24" s="38">
         <v>46113</v>
       </c>
     </row>
@@ -6326,13 +6332,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>818</v>
-      </c>
-      <c r="C25" s="24" t="s">
-        <v>819</v>
+        <v>816</v>
+      </c>
+      <c r="C25" s="24">
+        <v>2026</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="E25" s="41">
         <v>46113</v>
@@ -6343,16 +6349,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>4</v>
+        <v>819</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="E26" s="41">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -6360,13 +6366,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="E27" s="41">
         <v>46112</v>
@@ -6377,13 +6383,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>803</v>
-      </c>
-      <c r="C28" s="24">
-        <v>2026</v>
+        <v>801</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>4</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E28" s="41">
         <v>46112</v>
@@ -6394,13 +6400,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C29" s="24">
         <v>2026</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="E29" s="41">
         <v>46112</v>
@@ -6411,13 +6417,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C30" s="24">
         <v>2026</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="E30" s="41">
         <v>46112</v>
@@ -6428,13 +6434,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C31" s="24">
         <v>2026</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E31" s="41">
         <v>46112</v>
@@ -6445,16 +6451,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>793</v>
+        <v>809</v>
       </c>
       <c r="C32" s="24">
         <v>2026</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>794</v>
+        <v>810</v>
       </c>
       <c r="E32" s="41">
-        <v>46108</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -6462,13 +6468,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>795</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>4</v>
+        <v>793</v>
+      </c>
+      <c r="C33" s="24">
+        <v>2026</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E33" s="41">
         <v>46108</v>
@@ -6479,16 +6485,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C34" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E34" s="41">
-        <v>46104</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -6496,16 +6502,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>781</v>
-      </c>
-      <c r="E35" s="42">
-        <v>46100</v>
+        <v>798</v>
+      </c>
+      <c r="E35" s="41">
+        <v>46104</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -6513,16 +6519,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E36" s="42">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -6530,16 +6536,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="E37" s="42">
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -6547,16 +6553,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>761</v>
+        <v>784</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>762</v>
-      </c>
-      <c r="E38" s="42" t="s">
-        <v>756</v>
+        <v>785</v>
+      </c>
+      <c r="E38" s="42">
+        <v>46097</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -6564,13 +6570,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C39" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E39" s="42" t="s">
         <v>756</v>
@@ -6581,13 +6587,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D40" s="21" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E40" s="42" t="s">
         <v>756</v>
@@ -6598,33 +6604,33 @@
         <v>37</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D41" s="21" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E41" s="42" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>38</v>
       </c>
-      <c r="B42" t="s">
-        <v>588</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D42" t="s">
-        <v>384</v>
-      </c>
-      <c r="E42" s="38">
-        <v>46267</v>
+      <c r="B42" s="21" t="s">
+        <v>767</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -6632,16 +6638,16 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="E43" s="38">
-        <v>46144</v>
+        <v>46267</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -6649,50 +6655,50 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E44" s="38">
         <v>46144</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>591</v>
-      </c>
-      <c r="C45" s="8">
-        <v>2026</v>
+        <v>590</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E45" s="38">
-        <v>46051</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>592</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>4</v>
+        <v>591</v>
+      </c>
+      <c r="C46" s="8">
+        <v>2026</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>375</v>
       </c>
       <c r="E46" s="38">
-        <v>46038</v>
+        <v>46051</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -6700,16 +6706,16 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>593</v>
-      </c>
-      <c r="C47" s="8">
-        <v>2026</v>
+        <v>592</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D47" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E47" s="38">
-        <v>46025</v>
+        <v>46038</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -6717,16 +6723,16 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C48" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="38">
-        <v>46022</v>
+        <v>46025</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -6734,13 +6740,13 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>595</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>4</v>
+        <v>594</v>
+      </c>
+      <c r="C49" s="8">
+        <v>2025</v>
       </c>
       <c r="D49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E49" s="38">
         <v>46022</v>
@@ -6751,16 +6757,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>596</v>
-      </c>
-      <c r="C50" s="8">
-        <v>2025</v>
+        <v>595</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E50" s="38">
-        <v>46020</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -6768,16 +6774,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C51" s="8">
         <v>2025</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E51" s="38">
-        <v>46009</v>
+        <v>46020</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -6785,16 +6791,16 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>598</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>4</v>
+        <v>597</v>
+      </c>
+      <c r="C52" s="8">
+        <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E52" s="38">
-        <v>46000</v>
+        <v>46009</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -6802,16 +6808,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E53" s="38">
-        <v>45978</v>
+        <v>46000</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -6819,16 +6825,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E54" s="38">
-        <v>45965</v>
+        <v>45978</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -6836,16 +6842,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>601</v>
-      </c>
-      <c r="C55" s="8">
-        <v>2025</v>
+        <v>600</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E55" s="38">
-        <v>45951</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -6853,16 +6859,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C56" s="8">
         <v>2025</v>
       </c>
       <c r="D56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E56" s="38">
-        <v>45945</v>
+        <v>45951</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -6872,8 +6878,8 @@
       <c r="B57" t="s">
         <v>602</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>4</v>
+      <c r="C57" s="8">
+        <v>2025</v>
       </c>
       <c r="D57" t="s">
         <v>33</v>
@@ -6887,13 +6893,13 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E58" s="38">
         <v>45945</v>
@@ -6904,13 +6910,13 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E59" s="38">
         <v>45945</v>
@@ -6921,16 +6927,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E60" s="38">
-        <v>45944</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -6938,16 +6944,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E61" s="38">
-        <v>45940</v>
+        <v>45944</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -6955,13 +6961,13 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C62" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E62" s="38">
         <v>45940</v>
@@ -6972,16 +6978,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C63" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D63" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E63" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -6989,13 +6995,13 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E64" s="38">
         <v>45933</v>
@@ -7005,14 +7011,14 @@
       <c r="A65" s="1">
         <v>61</v>
       </c>
-      <c r="B65" s="8" t="s">
-        <v>610</v>
+      <c r="B65" t="s">
+        <v>609</v>
       </c>
       <c r="C65" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E65" s="38">
         <v>45933</v>
@@ -7023,13 +7029,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C66" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E66" s="38">
         <v>45933</v>
@@ -7040,16 +7046,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E67" s="38">
-        <v>45930</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -7057,16 +7063,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E68" s="38">
-        <v>45924</v>
+        <v>45930</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -7074,13 +7080,13 @@
         <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E69" s="38">
         <v>45924</v>
@@ -7091,13 +7097,13 @@
         <v>66</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E70" s="38">
         <v>45924</v>
@@ -7108,16 +7114,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>616</v>
-      </c>
-      <c r="C71" s="8">
-        <v>2025</v>
+        <v>615</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E71" s="38">
-        <v>45923</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -7125,16 +7131,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="C72" s="8" t="s">
-        <v>4</v>
+        <v>616</v>
+      </c>
+      <c r="C72" s="8">
+        <v>2025</v>
       </c>
       <c r="D72" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E72" s="38">
-        <v>45918</v>
+        <v>45923</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -7142,16 +7148,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E73" s="38">
-        <v>45908</v>
+        <v>45918</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -7159,16 +7165,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E74" s="38">
-        <v>45897</v>
+        <v>45908</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -7176,16 +7182,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D75" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E75" s="38">
-        <v>45891</v>
+        <v>45897</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -7193,13 +7199,13 @@
         <v>72</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E76" s="38">
         <v>45891</v>
@@ -7210,16 +7216,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E77" s="38">
-        <v>45888</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -7227,16 +7233,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E78" s="38">
-        <v>45880</v>
+        <v>45888</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -7244,16 +7250,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>69</v>
+        <v>623</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E79" s="38">
-        <v>45855</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -7261,16 +7267,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>624</v>
+        <v>69</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E80" s="38">
-        <v>45838</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -7278,13 +7284,13 @@
         <v>77</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E81" s="38">
         <v>45838</v>
@@ -7295,16 +7301,16 @@
         <v>78</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E82" s="38">
-        <v>45835</v>
+        <v>45838</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -7312,16 +7318,16 @@
         <v>79</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>75</v>
+        <v>626</v>
       </c>
       <c r="C83" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E83" s="38">
-        <v>45833</v>
+        <v>45835</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -7329,16 +7335,16 @@
         <v>80</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E84" s="38">
-        <v>45831</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -7346,16 +7352,16 @@
         <v>81</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D85" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="E85" s="38">
-        <v>45825</v>
+        <v>45831</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -7363,13 +7369,13 @@
         <v>82</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C86" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D86" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E86" s="38">
         <v>45825</v>
@@ -7380,13 +7386,13 @@
         <v>83</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E87" s="38">
         <v>45825</v>
@@ -7397,16 +7403,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D88" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E88" s="38">
-        <v>45808</v>
+        <v>45825</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -7414,16 +7420,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D89" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E89" s="38">
-        <v>45803</v>
+        <v>45808</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -7431,13 +7437,13 @@
         <v>86</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E90" s="38">
         <v>45803</v>
@@ -7448,13 +7454,13 @@
         <v>87</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E91" s="38">
         <v>45803</v>
@@ -7465,13 +7471,13 @@
         <v>88</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E92" s="38">
         <v>45803</v>
@@ -7482,13 +7488,13 @@
         <v>89</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E93" s="38">
         <v>45803</v>
@@ -7499,67 +7505,67 @@
         <v>90</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E94" s="38">
         <v>45803</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>91</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E95" s="38">
-        <v>45796</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45803</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>92</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E96" s="38">
         <v>45796</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>93</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C97" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E97" s="38">
-        <v>45794</v>
+        <v>45796</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -7567,16 +7573,16 @@
         <v>94</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E98" s="38">
-        <v>45779</v>
+        <v>45794</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -7584,16 +7590,16 @@
         <v>95</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D99" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E99" s="38">
-        <v>45770</v>
+        <v>45779</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -7601,16 +7607,16 @@
         <v>96</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E100" s="38">
-        <v>45762</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -7618,16 +7624,16 @@
         <v>97</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>644</v>
-      </c>
-      <c r="C101" s="8">
-        <v>2025</v>
+        <v>643</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E101" s="38">
-        <v>45749</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -7635,13 +7641,13 @@
         <v>98</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C102" s="8">
         <v>2025</v>
       </c>
       <c r="D102" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102" s="38">
         <v>45749</v>
@@ -7652,16 +7658,16 @@
         <v>99</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>4</v>
+        <v>645</v>
+      </c>
+      <c r="C103" s="8">
+        <v>2025</v>
       </c>
       <c r="D103" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E103" s="38">
-        <v>45748</v>
+        <v>45749</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -7669,16 +7675,16 @@
         <v>100</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="D104" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E104" s="38">
-        <v>45736</v>
+        <v>45748</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -7686,16 +7692,16 @@
         <v>101</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C105" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D105" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E105" s="38">
-        <v>45734</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -7703,16 +7709,16 @@
         <v>102</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E106" s="38">
-        <v>45726</v>
+        <v>45734</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -7720,13 +7726,13 @@
         <v>103</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="C107" s="8">
-        <v>2025</v>
+        <v>649</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E107" s="38">
         <v>45726</v>
@@ -7737,13 +7743,13 @@
         <v>104</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>114</v>
+        <v>650</v>
+      </c>
+      <c r="C108" s="8">
+        <v>2025</v>
       </c>
       <c r="D108" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E108" s="38">
         <v>45726</v>
@@ -7754,16 +7760,16 @@
         <v>105</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E109" s="38">
-        <v>45723</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
@@ -7771,16 +7777,16 @@
         <v>106</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E110" s="38">
-        <v>45721</v>
+        <v>45723</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -7788,16 +7794,16 @@
         <v>107</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E111" s="38">
-        <v>45698</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -7805,16 +7811,16 @@
         <v>108</v>
       </c>
       <c r="B112" s="8" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E112" s="38">
-        <v>45695</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -7822,33 +7828,33 @@
         <v>109</v>
       </c>
       <c r="B113" s="8" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E113" s="38">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>110</v>
       </c>
-      <c r="B114" t="s">
-        <v>587</v>
+      <c r="B114" s="8" t="s">
+        <v>656</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E114" s="38">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -7856,16 +7862,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C115" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E115" s="38">
-        <v>45686</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -7873,16 +7879,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C116" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E116" s="38">
-        <v>45681</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -7890,16 +7896,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E117" s="38">
-        <v>45678</v>
+        <v>45681</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -7907,16 +7913,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C118" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E118" s="38">
-        <v>45677</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -7924,13 +7930,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D119" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E119" s="38">
         <v>45677</v>
@@ -7941,16 +7947,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C120" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D120" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E120" s="38">
-        <v>45670</v>
+        <v>45677</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -7958,16 +7964,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C121" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D121" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E121" s="38">
-        <v>45661</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -7975,13 +7981,13 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C122" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D122" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E122" s="38">
         <v>45661</v>
@@ -7992,16 +7998,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E123" s="38">
-        <v>45659</v>
+        <v>45661</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -8009,16 +8015,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E124" s="38">
-        <v>45656</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -8026,13 +8032,13 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E125" s="38">
         <v>45656</v>
@@ -8043,16 +8049,16 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>575</v>
-      </c>
-      <c r="C126" s="8">
-        <v>2024</v>
+        <v>576</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E126" s="38">
-        <v>45652</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -8060,16 +8066,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>574</v>
-      </c>
-      <c r="C127" s="8" t="s">
-        <v>114</v>
+        <v>575</v>
+      </c>
+      <c r="C127" s="8">
+        <v>2024</v>
       </c>
       <c r="D127" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="E127" s="38">
-        <v>45650</v>
+        <v>45652</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -8077,16 +8083,16 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>157</v>
+        <v>119</v>
       </c>
       <c r="E128" s="38">
-        <v>45631</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -8094,16 +8100,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E129" s="38">
-        <v>45625</v>
+        <v>45631</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -8111,16 +8117,16 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C130" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E130" s="38">
-        <v>45622</v>
+        <v>45625</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -8128,16 +8134,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D131" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E131" s="38">
-        <v>45593</v>
+        <v>45622</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -8145,16 +8151,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E132" s="38">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -8162,13 +8168,13 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C133" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E133" s="38">
         <v>45588</v>
@@ -8179,16 +8185,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D134" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E134" s="38">
-        <v>45578</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -8196,16 +8202,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C135" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E135" s="38">
-        <v>45566</v>
+        <v>45578</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -8213,13 +8219,13 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E136" s="38">
         <v>45566</v>
@@ -8230,16 +8236,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E137" s="38">
-        <v>45565</v>
+        <v>45566</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -8247,16 +8253,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E138" s="38">
-        <v>45563</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -8264,16 +8270,16 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E139" s="38">
-        <v>45553</v>
+        <v>45563</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -8281,16 +8287,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C140" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="E140" s="38">
-        <v>45548</v>
+        <v>45553</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -8298,13 +8304,13 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D141" t="s">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="E141" s="38">
         <v>45548</v>
@@ -8315,16 +8321,16 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D142" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E142" s="38">
-        <v>45539</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -8332,16 +8338,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C143" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D143" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E143" s="38">
-        <v>45538</v>
+        <v>45539</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -8349,16 +8355,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C144" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D144" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E144" s="38">
-        <v>45537</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -8366,16 +8372,16 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D145" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E145" s="38">
-        <v>45523</v>
+        <v>45537</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -8383,16 +8389,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E146" s="38">
-        <v>45520</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -8400,16 +8406,16 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D147" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E147" s="38">
-        <v>45505</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -8417,16 +8423,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D148" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E148" s="38">
-        <v>45502</v>
+        <v>45505</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -8434,16 +8440,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D149" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E149" s="38">
-        <v>45478</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -8451,13 +8457,13 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D150" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E150" s="38">
         <v>45478</v>
@@ -8468,16 +8474,16 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D151" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E151" s="38">
-        <v>45462</v>
+        <v>45478</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -8485,16 +8491,16 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>204</v>
+        <v>550</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D152" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E152" s="38">
-        <v>45455</v>
+        <v>45462</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -8502,16 +8508,16 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>549</v>
+        <v>204</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D153" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E153" s="38">
-        <v>45454</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -8519,16 +8525,16 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D154" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E154" s="38">
-        <v>45449</v>
+        <v>45454</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -8536,16 +8542,16 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D155" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E155" s="38">
-        <v>45448</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -8553,16 +8559,16 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D156" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E156" s="38">
-        <v>45446</v>
+        <v>45448</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -8570,16 +8576,16 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C157" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D157" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E157" s="38">
-        <v>45432</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -8587,16 +8593,16 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D158" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E158" s="38">
-        <v>45420</v>
+        <v>45432</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -8604,16 +8610,16 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C159" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E159" s="38">
-        <v>45418</v>
+        <v>45420</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -8621,16 +8627,16 @@
         <v>156</v>
       </c>
       <c r="B160" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C160" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D160" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E160" s="38">
-        <v>45416</v>
+        <v>45418</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -8638,33 +8644,33 @@
         <v>157</v>
       </c>
       <c r="B161" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C161" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D161" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E161" s="38">
-        <v>45407</v>
+        <v>45416</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>158</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>540</v>
+      <c r="B162" t="s">
+        <v>541</v>
       </c>
       <c r="C162" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D162" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E162" s="38">
-        <v>45405</v>
+        <v>45407</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -8672,16 +8678,16 @@
         <v>159</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C163" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D163" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E163" s="38">
-        <v>45397</v>
+        <v>45405</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -8689,13 +8695,13 @@
         <v>160</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="C164" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D164" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E164" s="38">
         <v>45397</v>
@@ -8706,16 +8712,16 @@
         <v>161</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C165" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D165" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E165" s="38">
-        <v>45387</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -8723,13 +8729,13 @@
         <v>162</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C166" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D166" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E166" s="38">
         <v>45387</v>
@@ -8740,13 +8746,13 @@
         <v>163</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D167" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E167" s="38">
         <v>45387</v>
@@ -8757,16 +8763,16 @@
         <v>164</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>505</v>
+        <v>536</v>
       </c>
       <c r="C168" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D168" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E168" s="38">
-        <v>45385</v>
+        <v>45387</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -8774,16 +8780,16 @@
         <v>165</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>534</v>
+        <v>505</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D169" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E169" s="38">
-        <v>45384</v>
+        <v>45385</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -8791,33 +8797,33 @@
         <v>166</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>506</v>
+        <v>534</v>
       </c>
       <c r="C170" s="8" t="s">
-        <v>236</v>
+        <v>114</v>
       </c>
       <c r="D170" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E170" s="38">
-        <v>45378</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>167</v>
       </c>
-      <c r="B171" t="s">
-        <v>533</v>
+      <c r="B171" s="5" t="s">
+        <v>506</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D171" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E171" s="38">
-        <v>45373</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -8825,13 +8831,13 @@
         <v>168</v>
       </c>
       <c r="B172" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C172" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D172" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E172" s="38">
         <v>45373</v>
@@ -8842,16 +8848,16 @@
         <v>169</v>
       </c>
       <c r="B173" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C173" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D173" t="s">
-        <v>117</v>
+        <v>241</v>
       </c>
       <c r="E173" s="38">
-        <v>45369</v>
+        <v>45373</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -8859,16 +8865,16 @@
         <v>170</v>
       </c>
       <c r="B174" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C174" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D174" t="s">
-        <v>242</v>
+        <v>117</v>
       </c>
       <c r="E174" s="38">
-        <v>45367</v>
+        <v>45369</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -8876,13 +8882,13 @@
         <v>171</v>
       </c>
       <c r="B175" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C175" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D175" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E175" s="38">
         <v>45367</v>
@@ -8893,16 +8899,16 @@
         <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C176" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D176" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E176" s="38">
-        <v>45366</v>
+        <v>45367</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -8910,16 +8916,16 @@
         <v>173</v>
       </c>
       <c r="B177" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D177" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E177" s="38">
-        <v>45365</v>
+        <v>45366</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -8927,16 +8933,16 @@
         <v>174</v>
       </c>
       <c r="B178" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C178" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D178" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E178" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -8944,13 +8950,13 @@
         <v>175</v>
       </c>
       <c r="B179" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C179" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D179" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E179" s="38">
         <v>45362</v>
@@ -8961,13 +8967,13 @@
         <v>176</v>
       </c>
       <c r="B180" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C180" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D180" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E180" s="38">
         <v>45362</v>
@@ -8978,13 +8984,13 @@
         <v>177</v>
       </c>
       <c r="B181" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C181" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D181" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E181" s="38">
         <v>45362</v>
@@ -8995,16 +9001,16 @@
         <v>178</v>
       </c>
       <c r="B182" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C182" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D182" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E182" s="38">
-        <v>45359</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -9012,16 +9018,16 @@
         <v>179</v>
       </c>
       <c r="B183" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C183" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D183" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E183" s="38">
-        <v>45358</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -9029,13 +9035,13 @@
         <v>180</v>
       </c>
       <c r="B184" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E184" s="38">
         <v>45358</v>
@@ -9046,16 +9052,16 @@
         <v>181</v>
       </c>
       <c r="B185" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C185" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D185" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E185" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -9063,13 +9069,13 @@
         <v>182</v>
       </c>
       <c r="B186" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D186" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E186" s="38">
         <v>45357</v>
@@ -9080,16 +9086,16 @@
         <v>183</v>
       </c>
       <c r="B187" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C187" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D187" t="s">
-        <v>233</v>
+        <v>259</v>
       </c>
       <c r="E187" s="38">
-        <v>45352</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -9097,13 +9103,13 @@
         <v>184</v>
       </c>
       <c r="B188" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D188" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E188" s="38">
         <v>45352</v>
@@ -9114,13 +9120,13 @@
         <v>185</v>
       </c>
       <c r="B189" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C189" s="8" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="D189" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="E189" s="38">
         <v>45352</v>
@@ -9131,16 +9137,16 @@
         <v>186</v>
       </c>
       <c r="B190" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C190" s="8" t="s">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E190" s="38">
-        <v>45351</v>
+        <v>45352</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -9148,16 +9154,16 @@
         <v>187</v>
       </c>
       <c r="B191" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C191" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D191" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E191" s="38">
-        <v>45345</v>
+        <v>45351</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -9165,16 +9171,16 @@
         <v>188</v>
       </c>
       <c r="B192" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C192" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D192" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E192" s="38">
-        <v>45335</v>
+        <v>45345</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -9182,16 +9188,16 @@
         <v>189</v>
       </c>
       <c r="B193" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="C193" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D193" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E193" s="38">
-        <v>45334</v>
+        <v>45335</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -9199,50 +9205,50 @@
         <v>190</v>
       </c>
       <c r="B194" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C194" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D194" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="E194" s="38">
-        <v>45314</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>191</v>
       </c>
-      <c r="B195" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="C195" s="8">
-        <v>2023</v>
+      <c r="B195" t="s">
+        <v>511</v>
+      </c>
+      <c r="C195" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D195" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E195" s="38">
-        <v>45306</v>
+        <v>45314</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>192</v>
       </c>
-      <c r="B196" t="s">
-        <v>509</v>
-      </c>
-      <c r="C196" s="8" t="s">
-        <v>236</v>
+      <c r="B196" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="C196" s="8">
+        <v>2023</v>
       </c>
       <c r="D196" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E196" s="38">
-        <v>45294</v>
+        <v>45306</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -9250,15 +9256,32 @@
         <v>193</v>
       </c>
       <c r="B197" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D197" t="s">
+        <v>279</v>
+      </c>
+      <c r="E197" s="38">
+        <v>45294</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>194</v>
+      </c>
+      <c r="B198" t="s">
+        <v>508</v>
+      </c>
+      <c r="C198" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="D198" t="s">
         <v>281</v>
       </c>
-      <c r="E197" s="38">
+      <c r="E198" s="38">
         <v>45292</v>
       </c>
     </row>

--- a/backend/PDF_DOC/DGFT/ALL_PDF/DGFT POLICY - Copy.xlsx
+++ b/backend/PDF_DOC/DGFT/ALL_PDF/DGFT POLICY - Copy.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7BC6E8-2F68-4DB2-83C8-E490C9AAEB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01FF58C-9437-4F43-85C1-D56ACCE82172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PUBLIC NOTICE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="931">
   <si>
     <t>DGFT - PUBLIC NOTICE</t>
   </si>
@@ -2813,6 +2813,18 @@
   </si>
   <si>
     <t>PUBLIC NOTICE- 19/2026-27</t>
+  </si>
+  <si>
+    <t>TRADE NOTICE- 14/2026-27</t>
+  </si>
+  <si>
+    <t>Inputs on proposed amendment to Para 2.57 of FTP 2023 relating to de minimis exemption from RCMC requirements for low-value exports – regarding.</t>
+  </si>
+  <si>
+    <t>PUBLIC NOTICE- 22/2026-27</t>
+  </si>
+  <si>
+    <t>Inviting TRQ Applications under India – United Kingdom Comprehensive Economic and Trade Agreement (CETA) for Calendar Year (CY) 2026-reg.</t>
   </si>
 </sst>
 </file>
@@ -2851,7 +2863,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2906,6 +2918,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2928,7 +2946,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3086,6 +3104,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3366,7 +3392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O392"/>
+  <dimension ref="A1:O393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -3407,31 +3433,31 @@
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>924</v>
-      </c>
-      <c r="C5" s="63" t="s">
+      <c r="B5" s="71" t="s">
+        <v>929</v>
+      </c>
+      <c r="C5" s="72" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="65" t="s">
-        <v>913</v>
-      </c>
-      <c r="E5" s="64">
-        <v>46216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D5" s="74" t="s">
+        <v>930</v>
+      </c>
+      <c r="E5" s="73">
+        <v>46223</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C6" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D6" s="65" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="E6" s="64">
         <v>46216</v>
@@ -3441,34 +3467,34 @@
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="67" t="s">
-        <v>926</v>
-      </c>
-      <c r="C7" s="68" t="s">
+      <c r="B7" s="62" t="s">
+        <v>925</v>
+      </c>
+      <c r="C7" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D7" s="69" t="s">
-        <v>915</v>
-      </c>
-      <c r="E7" s="70">
-        <v>46212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="65" t="s">
+        <v>914</v>
+      </c>
+      <c r="E7" s="64">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="62" t="s">
-        <v>905</v>
-      </c>
-      <c r="C8" s="63" t="s">
+      <c r="B8" s="67" t="s">
+        <v>926</v>
+      </c>
+      <c r="C8" s="68" t="s">
         <v>819</v>
       </c>
-      <c r="D8" s="65" t="s">
-        <v>906</v>
-      </c>
-      <c r="E8" s="64">
-        <v>46204</v>
+      <c r="D8" s="69" t="s">
+        <v>915</v>
+      </c>
+      <c r="E8" s="70">
+        <v>46212</v>
       </c>
     </row>
     <row r="9" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3476,16 +3502,16 @@
         <v>5</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="C9" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="65" t="s">
-        <v>9</v>
+        <v>906</v>
       </c>
       <c r="E9" s="64">
-        <v>46177</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3493,16 +3519,16 @@
         <v>6</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C10" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D10" s="65" t="s">
-        <v>895</v>
+        <v>9</v>
       </c>
       <c r="E10" s="64">
-        <v>46175</v>
+        <v>46177</v>
       </c>
     </row>
     <row r="11" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3510,84 +3536,84 @@
         <v>7</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D11" s="65" t="s">
-        <v>28</v>
+        <v>895</v>
       </c>
       <c r="E11" s="64">
         <v>46175</v>
       </c>
     </row>
-    <row r="12" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>8</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C12" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D12" s="65" t="s">
-        <v>898</v>
+        <v>28</v>
       </c>
       <c r="E12" s="64">
-        <v>46174</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="58" t="s">
-        <v>886</v>
-      </c>
-      <c r="C13" s="59" t="s">
+      <c r="B13" s="62" t="s">
+        <v>897</v>
+      </c>
+      <c r="C13" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D13" s="61" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="60">
-        <v>46171</v>
+      <c r="D13" s="65" t="s">
+        <v>898</v>
+      </c>
+      <c r="E13" s="64">
+        <v>46174</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="54" t="s">
-        <v>882</v>
-      </c>
-      <c r="C14" s="55" t="s">
+      <c r="B14" s="58" t="s">
+        <v>886</v>
+      </c>
+      <c r="C14" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D14" s="57" t="s">
-        <v>883</v>
-      </c>
-      <c r="E14" s="56">
-        <v>46164</v>
+      <c r="D14" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="60">
+        <v>46171</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>863</v>
-      </c>
-      <c r="C15" s="35" t="s">
+      <c r="B15" s="54" t="s">
+        <v>882</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D15" s="36" t="s">
-        <v>864</v>
-      </c>
-      <c r="E15" s="49">
-        <v>46156</v>
+      <c r="D15" s="57" t="s">
+        <v>883</v>
+      </c>
+      <c r="E15" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -3595,561 +3621,561 @@
         <v>12</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>28</v>
+        <v>864</v>
       </c>
       <c r="E16" s="49">
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>13</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C17" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D17" s="36" t="s">
-        <v>867</v>
+        <v>28</v>
       </c>
       <c r="E17" s="49">
         <v>46153</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>14</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E18" s="49">
-        <v>46150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>870</v>
-      </c>
-      <c r="C19" s="51" t="s">
+      <c r="B19" s="34" t="s">
+        <v>868</v>
+      </c>
+      <c r="C19" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="D19" s="52" t="s">
-        <v>871</v>
-      </c>
-      <c r="E19" s="53">
-        <v>46147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="D19" s="36" t="s">
+        <v>869</v>
+      </c>
+      <c r="E19" s="49">
+        <v>46150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>859</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="B20" s="50" t="s">
+        <v>870</v>
+      </c>
+      <c r="C20" s="51" t="s">
         <v>819</v>
       </c>
-      <c r="D20" s="36" t="s">
-        <v>860</v>
-      </c>
-      <c r="E20" s="40">
-        <v>46146</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="52" t="s">
+        <v>871</v>
+      </c>
+      <c r="E20" s="53">
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>17</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>819</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E21" s="40">
-        <v>46142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>18</v>
       </c>
       <c r="B22" s="34" t="s">
-        <v>840</v>
-      </c>
-      <c r="C22" s="35">
-        <v>2026</v>
+        <v>861</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>819</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>841</v>
+        <v>862</v>
       </c>
       <c r="E22" s="40">
-        <v>46129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="32" t="s">
-        <v>836</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>837</v>
-      </c>
-      <c r="E23" s="48">
-        <v>46122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="34" t="s">
+        <v>840</v>
+      </c>
+      <c r="C23" s="35">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>841</v>
+      </c>
+      <c r="E23" s="40">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>20</v>
       </c>
       <c r="B24" s="32" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C24" s="26" t="s">
         <v>819</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E24" s="48">
         <v>46122</v>
       </c>
     </row>
-    <row r="25" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
-        <v>822</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="32" t="s">
+        <v>838</v>
+      </c>
+      <c r="C25" s="26" t="s">
         <v>819</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="E25" s="38">
-        <v>46119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D25" s="33" t="s">
+        <v>839</v>
+      </c>
+      <c r="E25" s="48">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>811</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>812</v>
-      </c>
-      <c r="E26" s="41">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>822</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>819</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E26" s="38">
+        <v>46119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>791</v>
-      </c>
-      <c r="C27" s="24">
-        <v>2025</v>
+        <v>811</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>8</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
       <c r="E27" s="41">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>786</v>
-      </c>
-      <c r="C28" s="24" t="s">
-        <v>4</v>
+        <v>791</v>
+      </c>
+      <c r="C28" s="24">
+        <v>2025</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>787</v>
+        <v>792</v>
       </c>
       <c r="E28" s="41">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D29" s="25" t="s">
-        <v>778</v>
+        <v>787</v>
       </c>
       <c r="E29" s="41">
-        <v>46087</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" s="31" t="s">
-        <v>779</v>
-      </c>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="C30" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="E30" s="45">
+      <c r="E30" s="41">
         <v>46087</v>
       </c>
-      <c r="F30" s="30"/>
-    </row>
-    <row r="31" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="21" t="s">
-        <v>754</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="B31" s="31" t="s">
+        <v>779</v>
+      </c>
+      <c r="C31" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="25" t="s">
-        <v>755</v>
-      </c>
-      <c r="E31" s="42" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D31" s="31" t="s">
+        <v>778</v>
+      </c>
+      <c r="E31" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F31" s="30"/>
+    </row>
+    <row r="32" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>28</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C32" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E32" s="42" t="s">
         <v>853</v>
       </c>
-      <c r="O32" s="21" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" s="21" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E33" s="42" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="O33" s="21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>30</v>
       </c>
-      <c r="B34" t="s">
-        <v>386</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E34" s="38">
-        <v>46328</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="C34" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="E34" s="42" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>4</v>
+        <v>382</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="E35" s="38">
-        <v>46144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D36" t="s">
-        <v>5</v>
+      <c r="D36" s="3" t="s">
+        <v>378</v>
       </c>
       <c r="E36" s="38">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E37" s="38">
-        <v>46038</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>390</v>
-      </c>
-      <c r="C38" s="8">
-        <v>2026</v>
+        <v>389</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E38" s="38">
-        <v>46031</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C39" s="8">
         <v>2026</v>
       </c>
       <c r="D39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="38">
         <v>46031</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C40" s="8">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E40" s="38">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46031</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>393</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>4</v>
+        <v>392</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2025</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E41" s="38">
-        <v>46010</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C42" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E42" s="38">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C43" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43" s="38">
         <v>46008</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D44" t="s">
-        <v>374</v>
+        <v>19</v>
       </c>
       <c r="E44" s="38">
-        <v>46002</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>397</v>
-      </c>
-      <c r="C45" s="8">
-        <v>2025</v>
+        <v>396</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>20</v>
+        <v>374</v>
       </c>
       <c r="E45" s="38">
-        <v>46001</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C46" s="8">
         <v>2025</v>
       </c>
       <c r="D46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E46" s="38">
         <v>46001</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>399</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>4</v>
+        <v>398</v>
+      </c>
+      <c r="C47" s="8">
+        <v>2025</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E47" s="38">
-        <v>45992</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C48" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E48" s="38">
         <v>45992</v>
@@ -4160,16 +4186,16 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>401</v>
-      </c>
-      <c r="C49" s="8">
-        <v>2025</v>
+        <v>400</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D49" t="s">
-        <v>373</v>
+        <v>24</v>
       </c>
       <c r="E49" s="38">
-        <v>45981</v>
+        <v>45992</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -4177,16 +4203,16 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>402</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>4</v>
+        <v>401</v>
+      </c>
+      <c r="C50" s="8">
+        <v>2025</v>
       </c>
       <c r="D50" t="s">
-        <v>27</v>
+        <v>373</v>
       </c>
       <c r="E50" s="38">
-        <v>45959</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,16 +4220,16 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>403</v>
-      </c>
-      <c r="C51" s="8">
-        <v>2025</v>
+        <v>402</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E51" s="38">
-        <v>45958</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -4211,13 +4237,13 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C52" s="8">
         <v>2025</v>
       </c>
       <c r="D52" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E52" s="38">
         <v>45958</v>
@@ -4228,16 +4254,16 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>405</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="C53" s="8">
+        <v>2025</v>
       </c>
       <c r="D53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E53" s="38">
-        <v>45953</v>
+        <v>45958</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,16 +4271,16 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E54" s="38">
-        <v>45952</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -4262,16 +4288,16 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D55" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E55" s="38">
-        <v>45945</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -4279,16 +4305,16 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>38</v>
+        <v>407</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D56" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E56" s="38">
-        <v>45940</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -4296,13 +4322,13 @@
         <v>53</v>
       </c>
       <c r="B57" t="s">
-        <v>408</v>
+        <v>38</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E57" s="38">
         <v>45940</v>
@@ -4313,16 +4339,16 @@
         <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C58" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D58" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E58" s="38">
-        <v>45933</v>
+        <v>45940</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,16 +4356,16 @@
         <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C59" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E59" s="38">
-        <v>45931</v>
+        <v>45933</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -4347,16 +4373,16 @@
         <v>56</v>
       </c>
       <c r="B60" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C60" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E60" s="38">
-        <v>45909</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -4364,16 +4390,16 @@
         <v>57</v>
       </c>
       <c r="B61" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C61" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E61" s="38">
-        <v>45903</v>
+        <v>45909</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -4381,16 +4407,16 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>413</v>
-      </c>
-      <c r="C62" s="8">
-        <v>2025</v>
+        <v>412</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D62" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E62" s="38">
-        <v>45895</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -4398,16 +4424,16 @@
         <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>414</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>4</v>
+        <v>413</v>
+      </c>
+      <c r="C63" s="8">
+        <v>2025</v>
       </c>
       <c r="D63" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E63" s="38">
-        <v>45891</v>
+        <v>45895</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -4415,16 +4441,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C64" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E64" s="38">
-        <v>45870</v>
+        <v>45891</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,16 +4458,16 @@
         <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>416</v>
-      </c>
-      <c r="C65" s="8">
-        <v>2025</v>
+        <v>415</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D65" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E65" s="38">
-        <v>45868</v>
+        <v>45870</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -4449,16 +4475,16 @@
         <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>417</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>4</v>
+        <v>416</v>
+      </c>
+      <c r="C66" s="8">
+        <v>2025</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E66" s="38">
-        <v>45867</v>
+        <v>45868</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -4466,16 +4492,16 @@
         <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C67" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D67" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E67" s="38">
-        <v>45860</v>
+        <v>45867</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -4483,16 +4509,16 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C68" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E68" s="38">
-        <v>45846</v>
+        <v>45860</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,16 +4526,16 @@
         <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C69" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D69" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E69" s="38">
-        <v>45833</v>
+        <v>45846</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -4517,13 +4543,13 @@
         <v>66</v>
       </c>
       <c r="B70" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C70" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E70" s="38">
         <v>45833</v>
@@ -4534,16 +4560,16 @@
         <v>67</v>
       </c>
       <c r="B71" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C71" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E71" s="38">
-        <v>45820</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -4551,13 +4577,13 @@
         <v>68</v>
       </c>
       <c r="B72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C72" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D72" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E72" s="38">
         <v>45820</v>
@@ -4568,16 +4594,16 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C73" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E73" s="38">
-        <v>45818</v>
+        <v>45820</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -4585,16 +4611,16 @@
         <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>425</v>
-      </c>
-      <c r="C74" s="8">
-        <v>2025</v>
+        <v>424</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E74" s="38">
-        <v>45807</v>
+        <v>45818</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4602,16 +4628,16 @@
         <v>71</v>
       </c>
       <c r="B75" t="s">
-        <v>426</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>4</v>
+        <v>425</v>
+      </c>
+      <c r="C75" s="8">
+        <v>2025</v>
       </c>
       <c r="D75" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E75" s="38">
-        <v>45793</v>
+        <v>45807</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -4619,16 +4645,16 @@
         <v>72</v>
       </c>
       <c r="B76" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C76" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E76" s="38">
-        <v>45784</v>
+        <v>45793</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -4636,16 +4662,16 @@
         <v>73</v>
       </c>
       <c r="B77" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C77" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E77" s="38">
-        <v>45783</v>
+        <v>45784</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -4653,13 +4679,13 @@
         <v>74</v>
       </c>
       <c r="B78" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C78" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D78" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E78" s="38">
         <v>45783</v>
@@ -4670,16 +4696,16 @@
         <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D79" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E79" s="38">
-        <v>45771</v>
+        <v>45783</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -4687,16 +4713,16 @@
         <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D80" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E80" s="38">
-        <v>45762</v>
+        <v>45771</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -4704,16 +4730,16 @@
         <v>77</v>
       </c>
       <c r="B81" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E81" s="38">
-        <v>45750</v>
+        <v>45762</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4721,16 +4747,16 @@
         <v>78</v>
       </c>
       <c r="B82" t="s">
-        <v>433</v>
-      </c>
-      <c r="C82" s="8">
-        <v>2025</v>
+        <v>432</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E82" s="38">
-        <v>45744</v>
+        <v>45750</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -4738,16 +4764,16 @@
         <v>79</v>
       </c>
       <c r="B83" t="s">
-        <v>110</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>4</v>
+        <v>433</v>
+      </c>
+      <c r="C83" s="8">
+        <v>2025</v>
       </c>
       <c r="D83" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E83" s="38">
-        <v>45743</v>
+        <v>45744</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -4755,13 +4781,13 @@
         <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>434</v>
+        <v>110</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E84" s="38">
         <v>45743</v>
@@ -4772,16 +4798,16 @@
         <v>81</v>
       </c>
       <c r="B85" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D85" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E85" s="38">
-        <v>45735</v>
+        <v>45743</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4789,16 +4815,16 @@
         <v>82</v>
       </c>
       <c r="B86" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D86" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E86" s="38">
-        <v>45726</v>
+        <v>45735</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -4806,16 +4832,16 @@
         <v>83</v>
       </c>
       <c r="B87" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D87" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E87" s="38">
-        <v>45719</v>
+        <v>45726</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -4823,16 +4849,16 @@
         <v>84</v>
       </c>
       <c r="B88" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E88" s="38">
-        <v>45700</v>
+        <v>45719</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -4840,16 +4866,16 @@
         <v>85</v>
       </c>
       <c r="B89" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C89" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E89" s="38">
-        <v>45695</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4857,16 +4883,16 @@
         <v>86</v>
       </c>
       <c r="B90" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C90" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D90" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E90" s="38">
-        <v>45694</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -4874,16 +4900,16 @@
         <v>87</v>
       </c>
       <c r="B91" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C91" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D91" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E91" s="38">
-        <v>45692</v>
+        <v>45694</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4891,16 +4917,16 @@
         <v>88</v>
       </c>
       <c r="B92" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C92" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E92" s="38">
-        <v>45688</v>
+        <v>45692</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -4908,16 +4934,16 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D93" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E93" s="38">
-        <v>45684</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -4925,16 +4951,16 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D94" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E94" s="38">
-        <v>45678</v>
+        <v>45684</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -4942,16 +4968,16 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D95" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E95" s="38">
-        <v>45672</v>
+        <v>45678</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4959,13 +4985,13 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D96" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E96" s="38">
         <v>45672</v>
@@ -4993,16 +5019,16 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D98" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E98" s="38">
-        <v>45662</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -5010,16 +5036,16 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C99" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D99" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E99" s="38">
-        <v>45660</v>
+        <v>45662</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -5027,16 +5053,16 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C100" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D100" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E100" s="38">
-        <v>45659</v>
+        <v>45660</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -5044,16 +5070,16 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>450</v>
-      </c>
-      <c r="C101" s="8">
-        <v>2024</v>
+        <v>449</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D101" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E101" s="38">
-        <v>45653</v>
+        <v>45659</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -5061,16 +5087,16 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C102" s="8">
         <v>2024</v>
       </c>
       <c r="D102" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E102" s="38">
-        <v>45650</v>
+        <v>45653</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -5078,16 +5104,16 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>452</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>114</v>
+        <v>451</v>
+      </c>
+      <c r="C103" s="8">
+        <v>2024</v>
       </c>
       <c r="D103" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E103" s="38">
-        <v>45643</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -5095,16 +5121,16 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>284</v>
+        <v>452</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D104" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E104" s="38">
-        <v>45639</v>
+        <v>45643</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -5112,16 +5138,16 @@
         <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>453</v>
+        <v>284</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D105" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E105" s="38">
-        <v>45610</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -5129,16 +5155,16 @@
         <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C106" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D106" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E106" s="38">
-        <v>45609</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -5146,16 +5172,16 @@
         <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>455</v>
-      </c>
-      <c r="C107" s="8">
-        <v>2024</v>
+        <v>454</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D107" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E107" s="38">
-        <v>45601</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -5163,16 +5189,16 @@
         <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>456</v>
-      </c>
-      <c r="C108" s="8" t="s">
-        <v>114</v>
+        <v>455</v>
+      </c>
+      <c r="C108" s="8">
+        <v>2024</v>
       </c>
       <c r="D108" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E108" s="38">
-        <v>45597</v>
+        <v>45601</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
@@ -5180,13 +5206,13 @@
         <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C109" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D109" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E109" s="38">
         <v>45597</v>
@@ -5197,16 +5223,16 @@
         <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C110" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D110" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E110" s="38">
-        <v>45593</v>
+        <v>45597</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
@@ -5214,16 +5240,16 @@
         <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C111" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D111" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E111" s="38">
-        <v>45588</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
@@ -5231,16 +5257,16 @@
         <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C112" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D112" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E112" s="38">
-        <v>45572</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -5248,16 +5274,16 @@
         <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C113" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D113" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="E113" s="38">
-        <v>45562</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -5265,16 +5291,16 @@
         <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C114" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D114" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E114" s="38">
-        <v>45555</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -5282,16 +5308,16 @@
         <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>463</v>
-      </c>
-      <c r="C115" s="8">
-        <v>2024</v>
+        <v>462</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D115" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E115" s="38">
-        <v>45547</v>
+        <v>45555</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -5299,16 +5325,16 @@
         <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>464</v>
-      </c>
-      <c r="C116" s="8" t="s">
-        <v>114</v>
+        <v>463</v>
+      </c>
+      <c r="C116" s="8">
+        <v>2024</v>
       </c>
       <c r="D116" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E116" s="38">
-        <v>45538</v>
+        <v>45547</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -5316,16 +5342,16 @@
         <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C117" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D117" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E117" s="38">
-        <v>45534</v>
+        <v>45538</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -5333,16 +5359,16 @@
         <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D118" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E118" s="38">
-        <v>45533</v>
+        <v>45534</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -5350,13 +5376,13 @@
         <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C119" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D119" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E119" s="38">
         <v>45533</v>
@@ -5367,16 +5393,16 @@
         <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>468</v>
-      </c>
-      <c r="C120" s="8">
-        <v>2024</v>
+        <v>467</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>112</v>
       </c>
       <c r="D120" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E120" s="38">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -5384,16 +5410,16 @@
         <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C121" s="8">
         <v>2024</v>
       </c>
       <c r="D121" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E121" s="38">
-        <v>45518</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -5401,16 +5427,16 @@
         <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>470</v>
-      </c>
-      <c r="C122" s="8" t="s">
-        <v>114</v>
+        <v>469</v>
+      </c>
+      <c r="C122" s="8">
+        <v>2024</v>
       </c>
       <c r="D122" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E122" s="38">
-        <v>45502</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -5418,16 +5444,16 @@
         <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C123" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D123" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E123" s="38">
-        <v>45498</v>
+        <v>45502</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -5435,16 +5461,16 @@
         <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D124" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E124" s="38">
-        <v>45489</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -5452,16 +5478,16 @@
         <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C125" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D125" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E125" s="38">
-        <v>45469</v>
+        <v>45489</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -5469,13 +5495,13 @@
         <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D126" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E126" s="38">
         <v>45469</v>
@@ -5486,16 +5512,16 @@
         <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>202</v>
+        <v>474</v>
       </c>
       <c r="C127" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D127" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E127" s="38">
-        <v>45455</v>
+        <v>45469</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -5503,13 +5529,13 @@
         <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>475</v>
+        <v>202</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D128" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E128" s="38">
         <v>45455</v>
@@ -5520,16 +5546,16 @@
         <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C129" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D129" t="s">
-        <v>162</v>
+        <v>206</v>
       </c>
       <c r="E129" s="38">
-        <v>45449</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -5537,13 +5563,13 @@
         <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>477</v>
-      </c>
-      <c r="C130" s="8">
-        <v>2024</v>
+        <v>476</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>114</v>
       </c>
       <c r="D130" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="E130" s="38">
         <v>45449</v>
@@ -5554,16 +5580,16 @@
         <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>478</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>114</v>
+        <v>477</v>
+      </c>
+      <c r="C131" s="8">
+        <v>2024</v>
       </c>
       <c r="D131" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E131" s="38">
-        <v>45446</v>
+        <v>45449</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -5571,16 +5597,16 @@
         <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C132" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D132" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E132" s="38">
-        <v>45441</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -5588,16 +5614,16 @@
         <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D133" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E133" s="38">
-        <v>45440</v>
+        <v>45441</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -5605,16 +5631,16 @@
         <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C134" s="8" t="s">
         <v>112</v>
       </c>
       <c r="D134" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E134" s="38">
-        <v>45439</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -5622,16 +5648,16 @@
         <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C135" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D135" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E135" s="38">
-        <v>45422</v>
+        <v>45439</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -5639,16 +5665,16 @@
         <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D136" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E136" s="38">
-        <v>45415</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -5656,16 +5682,16 @@
         <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>285</v>
+        <v>483</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D137" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E137" s="38">
-        <v>45411</v>
+        <v>45415</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -5673,16 +5699,16 @@
         <v>134</v>
       </c>
       <c r="B138" t="s">
-        <v>484</v>
+        <v>285</v>
       </c>
       <c r="C138" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D138" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E138" s="38">
-        <v>45391</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -5690,13 +5716,13 @@
         <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D139" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E139" s="38">
         <v>45391</v>
@@ -5707,16 +5733,16 @@
         <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C140" s="8" t="s">
-        <v>235</v>
+        <v>114</v>
       </c>
       <c r="D140" t="s">
-        <v>105</v>
+        <v>229</v>
       </c>
       <c r="E140" s="38">
-        <v>45379</v>
+        <v>45391</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -5724,16 +5750,16 @@
         <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D141" t="s">
-        <v>238</v>
+        <v>105</v>
       </c>
       <c r="E141" s="38">
-        <v>45378</v>
+        <v>45379</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -5741,13 +5767,13 @@
         <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D142" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E142" s="38">
         <v>45378</v>
@@ -5758,16 +5784,16 @@
         <v>139</v>
       </c>
       <c r="B143" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C143" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D143" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="E143" s="38">
-        <v>45365</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -5775,16 +5801,16 @@
         <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C144" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D144" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E144" s="38">
-        <v>45362</v>
+        <v>45365</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -5792,13 +5818,13 @@
         <v>141</v>
       </c>
       <c r="B145" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="C145" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D145" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E145" s="38">
         <v>45362</v>
@@ -5809,16 +5835,16 @@
         <v>142</v>
       </c>
       <c r="B146" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D146" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E146" s="38">
-        <v>45358</v>
+        <v>45362</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -5826,13 +5852,13 @@
         <v>143</v>
       </c>
       <c r="B147" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D147" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E147" s="38">
         <v>45358</v>
@@ -5843,16 +5869,16 @@
         <v>144</v>
       </c>
       <c r="B148" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C148" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D148" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E148" s="38">
-        <v>45357</v>
+        <v>45358</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -5860,16 +5886,16 @@
         <v>145</v>
       </c>
       <c r="B149" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C149" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D149" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E149" s="38">
-        <v>45350</v>
+        <v>45357</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -5877,16 +5903,16 @@
         <v>146</v>
       </c>
       <c r="B150" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C150" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D150" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E150" s="38">
-        <v>45344</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -5894,16 +5920,16 @@
         <v>147</v>
       </c>
       <c r="B151" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C151" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D151" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E151" s="38">
-        <v>45336</v>
+        <v>45344</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -5911,13 +5937,13 @@
         <v>148</v>
       </c>
       <c r="B152" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C152" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D152" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E152" s="38">
         <v>45336</v>
@@ -5928,13 +5954,13 @@
         <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C153" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D153" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E153" s="38">
         <v>45336</v>
@@ -5945,16 +5971,16 @@
         <v>150</v>
       </c>
       <c r="B154" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D154" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E154" s="38">
-        <v>45334</v>
+        <v>45336</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -5962,16 +5988,16 @@
         <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>222</v>
+        <v>495</v>
       </c>
       <c r="C155" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D155" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E155" s="38">
-        <v>45331</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -5979,16 +6005,16 @@
         <v>152</v>
       </c>
       <c r="B156" t="s">
-        <v>494</v>
+        <v>222</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>236</v>
       </c>
       <c r="D156" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E156" s="38">
-        <v>45324</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -5996,16 +6022,16 @@
         <v>153</v>
       </c>
       <c r="B157" t="s">
-        <v>493</v>
-      </c>
-      <c r="C157" s="8">
-        <v>2024</v>
+        <v>494</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>236</v>
       </c>
       <c r="D157" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E157" s="38">
-        <v>45322</v>
+        <v>45324</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -6013,16 +6039,16 @@
         <v>154</v>
       </c>
       <c r="B158" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C158" s="8">
         <v>2024</v>
       </c>
       <c r="D158" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E158" s="38">
-        <v>45303</v>
+        <v>45322</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -6030,20 +6056,34 @@
         <v>155</v>
       </c>
       <c r="B159" t="s">
+        <v>492</v>
+      </c>
+      <c r="C159" s="8">
+        <v>2024</v>
+      </c>
+      <c r="D159" t="s">
+        <v>278</v>
+      </c>
+      <c r="E159" s="38">
+        <v>45303</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>156</v>
+      </c>
+      <c r="B160" t="s">
         <v>491</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C160" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="D159" t="s">
+      <c r="D160" t="s">
         <v>280</v>
       </c>
-      <c r="E159" s="38">
+      <c r="E160" s="38">
         <v>45294</v>
       </c>
-    </row>
-    <row r="314" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B314" s="2"/>
     </row>
     <row r="315" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B315" s="2"/>
@@ -6057,17 +6097,17 @@
     <row r="318" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B318" s="2"/>
     </row>
-    <row r="321" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B321" s="2"/>
-    </row>
-    <row r="326" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B326" s="2"/>
-    </row>
-    <row r="329" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B329" s="2"/>
-    </row>
-    <row r="331" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B331" s="2"/>
+    <row r="319" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B319" s="2"/>
+    </row>
+    <row r="322" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B322" s="2"/>
+    </row>
+    <row r="327" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B327" s="2"/>
+    </row>
+    <row r="330" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B330" s="2"/>
     </row>
     <row r="332" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B332" s="2"/>
@@ -6075,8 +6115,8 @@
     <row r="333" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B333" s="2"/>
     </row>
-    <row r="335" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B335" s="2"/>
+    <row r="334" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B334" s="2"/>
     </row>
     <row r="336" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B336" s="2"/>
@@ -6090,15 +6130,18 @@
     <row r="339" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B339" s="2"/>
     </row>
-    <row r="341" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B341" s="2"/>
-    </row>
-    <row r="392" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B392" s="2"/>
+    <row r="340" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B340" s="2"/>
+    </row>
+    <row r="342" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B342" s="2"/>
+    </row>
+    <row r="393" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B393" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A34:E157">
-    <sortCondition descending="1" sortBy="icon" ref="E34:E157"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A35:E158">
+    <sortCondition descending="1" sortBy="icon" ref="E35:E158"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -42811,7 +42854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="20"/>
@@ -42860,17 +42903,17 @@
       <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="62" t="s">
-        <v>918</v>
-      </c>
-      <c r="C5" s="63" t="s">
+      <c r="B5" s="71" t="s">
+        <v>927</v>
+      </c>
+      <c r="C5" s="72" t="s">
         <v>819</v>
       </c>
-      <c r="D5" s="62" t="s">
-        <v>919</v>
-      </c>
-      <c r="E5" s="64">
-        <v>46217</v>
+      <c r="D5" s="71" t="s">
+        <v>928</v>
+      </c>
+      <c r="E5" s="73">
+        <v>46223</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -42878,13 +42921,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="62" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C6" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D6" s="62" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="E6" s="64">
         <v>46217</v>
@@ -42895,16 +42938,16 @@
         <v>3</v>
       </c>
       <c r="B7" s="62" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="C7" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D7" s="62" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="E7" s="64">
-        <v>46216</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -42912,16 +42955,16 @@
         <v>4</v>
       </c>
       <c r="B8" s="62" t="s">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="C8" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="E8" s="64">
-        <v>46204</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -42929,13 +42972,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C9" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D9" s="62" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="E9" s="64">
         <v>46204</v>
@@ -42946,13 +42989,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="62" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C10" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D10" s="62" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="E10" s="64">
         <v>46204</v>
@@ -42963,50 +43006,50 @@
         <v>7</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="C11" s="63" t="s">
         <v>819</v>
       </c>
       <c r="D11" s="62" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="E11" s="64">
-        <v>46176</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>8</v>
       </c>
-      <c r="B12" s="58" t="s">
-        <v>884</v>
-      </c>
-      <c r="C12" s="59" t="s">
+      <c r="B12" s="62" t="s">
+        <v>899</v>
+      </c>
+      <c r="C12" s="63" t="s">
         <v>819</v>
       </c>
-      <c r="D12" s="58" t="s">
-        <v>885</v>
-      </c>
-      <c r="E12" s="60">
-        <v>46171</v>
+      <c r="D12" s="62" t="s">
+        <v>900</v>
+      </c>
+      <c r="E12" s="64">
+        <v>46176</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>9</v>
       </c>
-      <c r="B13" s="54" t="s">
-        <v>878</v>
-      </c>
-      <c r="C13" s="55" t="s">
+      <c r="B13" s="58" t="s">
+        <v>884</v>
+      </c>
+      <c r="C13" s="59" t="s">
         <v>819</v>
       </c>
-      <c r="D13" s="54" t="s">
-        <v>879</v>
-      </c>
-      <c r="E13" s="56">
-        <v>46164</v>
+      <c r="D13" s="58" t="s">
+        <v>885</v>
+      </c>
+      <c r="E13" s="60">
+        <v>46171</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -43014,13 +43057,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="54" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C14" s="55" t="s">
         <v>819</v>
       </c>
       <c r="D14" s="54" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E14" s="56">
         <v>46164</v>
@@ -43030,17 +43073,17 @@
       <c r="A15" s="19">
         <v>11</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>876</v>
-      </c>
-      <c r="C15" s="35" t="s">
+      <c r="B15" s="54" t="s">
+        <v>880</v>
+      </c>
+      <c r="C15" s="55" t="s">
         <v>819</v>
       </c>
-      <c r="D15" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="E15" s="49">
-        <v>46155</v>
+      <c r="D15" s="54" t="s">
+        <v>881</v>
+      </c>
+      <c r="E15" s="56">
+        <v>46164</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -43048,571 +43091,571 @@
         <v>12</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>850</v>
+        <v>876</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>814</v>
+        <v>819</v>
       </c>
       <c r="D16" s="34" t="s">
-        <v>851</v>
-      </c>
-      <c r="E16" s="40">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>877</v>
+      </c>
+      <c r="E16" s="49">
+        <v>46155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>13</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="E17" s="40">
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="19">
         <v>14</v>
       </c>
-      <c r="B18" s="21" t="s">
-        <v>813</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>814</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>815</v>
-      </c>
-      <c r="E18" s="41">
-        <v>46113</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="34" t="s">
+        <v>848</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>819</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>849</v>
+      </c>
+      <c r="E18" s="40">
+        <v>46132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19">
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>789</v>
+        <v>813</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>8</v>
+        <v>814</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="E19" s="41">
-        <v>46101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="19">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="s">
-        <v>774</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="29" t="s">
-        <v>775</v>
-      </c>
-      <c r="E20" s="45">
-        <v>46087</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="21" t="s">
+        <v>789</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>790</v>
+      </c>
+      <c r="E20" s="41">
+        <v>46101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="19">
         <v>17</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C21" s="28" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E21" s="45">
         <v>46087</v>
       </c>
       <c r="F21" s="30"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19">
         <v>18</v>
       </c>
-      <c r="B22" t="s">
-        <v>773</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="27" t="s">
+        <v>776</v>
+      </c>
+      <c r="C22" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="D22" t="s">
-        <v>772</v>
-      </c>
-      <c r="E22" s="38">
-        <v>46084</v>
-      </c>
-      <c r="F22" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D22" s="29" t="s">
+        <v>777</v>
+      </c>
+      <c r="E22" s="45">
+        <v>46087</v>
+      </c>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19">
         <v>19</v>
       </c>
-      <c r="B23" s="21" t="s">
-        <v>744</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>745</v>
-      </c>
-      <c r="E23" s="41">
-        <v>46073</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>773</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D23" t="s">
+        <v>772</v>
+      </c>
+      <c r="E23" s="38">
+        <v>46084</v>
+      </c>
+      <c r="F23" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19">
         <v>20</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E24" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19">
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C25" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E25" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19">
         <v>22</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C26" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E26" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19">
         <v>23</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E27" s="41">
         <v>46073</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19">
         <v>24</v>
       </c>
-      <c r="B28" t="s">
-        <v>681</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="B28" s="21" t="s">
+        <v>752</v>
+      </c>
+      <c r="C28" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="D28" t="s">
-        <v>385</v>
-      </c>
-      <c r="E28" s="38">
-        <v>46267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D28" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="E28" s="41">
+        <v>46073</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="19">
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C29" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E29" s="38">
-        <v>46175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="19">
         <v>26</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>683</v>
+      <c r="B30" t="s">
+        <v>682</v>
       </c>
       <c r="C30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="E30" s="46">
-        <v>46045</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D30" t="s">
+        <v>380</v>
+      </c>
+      <c r="E30" s="38">
+        <v>46175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
         <v>27</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>684</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="B31" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E31" s="47">
-        <v>46024</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E31" s="46">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
         <v>28</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E32" s="47">
         <v>46024</v>
       </c>
-      <c r="H32" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
         <v>29</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E33" s="47">
-        <v>46022</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46024</v>
+      </c>
+      <c r="H33" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
         <v>30</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E34" s="47">
-        <v>45986</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
         <v>31</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="17" t="s">
-        <v>319</v>
+      <c r="D35" s="16" t="s">
+        <v>318</v>
       </c>
       <c r="E35" s="47">
-        <v>45961</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45986</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
         <v>32</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E36" s="47">
-        <v>45959</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>33</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>321</v>
+      <c r="D37" s="17" t="s">
+        <v>320</v>
       </c>
       <c r="E37" s="47">
         <v>45959</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
         <v>34</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E38" s="47">
-        <v>45957</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45959</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
         <v>35</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C39" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="17" t="s">
-        <v>323</v>
+      <c r="D39" s="16" t="s">
+        <v>322</v>
       </c>
       <c r="E39" s="47">
-        <v>45930</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45957</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
         <v>36</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C40" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="16" t="s">
-        <v>324</v>
+      <c r="D40" s="17" t="s">
+        <v>323</v>
       </c>
       <c r="E40" s="47">
-        <v>45924</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45930</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
         <v>37</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>743</v>
-      </c>
-      <c r="C41" s="16">
-        <v>2025</v>
+        <v>693</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E41" s="47">
-        <v>45896</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45924</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19">
         <v>38</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>4</v>
+        <v>743</v>
+      </c>
+      <c r="C42" s="16">
+        <v>2025</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E42" s="47">
-        <v>45866</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45896</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19">
         <v>39</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C43" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E43" s="47">
-        <v>45860</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45866</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19">
         <v>40</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E44" s="47">
-        <v>45852</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45860</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19">
         <v>41</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="C45" s="16">
-        <v>2025</v>
-      </c>
-      <c r="D45" s="17" t="s">
-        <v>329</v>
+        <v>740</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>328</v>
       </c>
       <c r="E45" s="47">
-        <v>45840</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45852</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19">
         <v>42</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>330</v>
+        <v>739</v>
+      </c>
+      <c r="C46" s="16">
+        <v>2025</v>
+      </c>
+      <c r="D46" s="17" t="s">
+        <v>329</v>
       </c>
       <c r="E46" s="47">
-        <v>45826</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45840</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19">
         <v>43</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C47" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E47" s="47">
-        <v>45821</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>45826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19">
         <v>44</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C48" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E48" s="47">
-        <v>45776</v>
+        <v>45821</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43620,16 +43663,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>735</v>
-      </c>
-      <c r="C49" s="16">
-        <v>2025</v>
+        <v>736</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E49" s="47">
-        <v>45770</v>
+        <v>45776</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43637,16 +43680,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>734</v>
-      </c>
-      <c r="C50" s="16" t="s">
-        <v>4</v>
+        <v>735</v>
+      </c>
+      <c r="C50" s="16">
+        <v>2025</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E50" s="47">
-        <v>45768</v>
+        <v>45770</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43654,16 +43697,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C51" s="16" t="s">
         <v>4</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E51" s="47">
-        <v>45758</v>
+        <v>45768</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43671,16 +43714,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D52" s="17" t="s">
-        <v>336</v>
+        <v>4</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>335</v>
       </c>
       <c r="E52" s="47">
-        <v>45741</v>
+        <v>45758</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43688,16 +43731,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C53" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="D53" s="16" t="s">
-        <v>337</v>
+      <c r="D53" s="17" t="s">
+        <v>336</v>
       </c>
       <c r="E53" s="47">
-        <v>45736</v>
+        <v>45741</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43705,16 +43748,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E54" s="47">
-        <v>45728</v>
+        <v>45736</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43722,16 +43765,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C55" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D55" s="16" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E55" s="47">
-        <v>45716</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43739,16 +43782,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D56" s="16" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E56" s="47">
-        <v>45701</v>
+        <v>45716</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43756,16 +43799,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C57" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E57" s="47">
-        <v>45700</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43773,16 +43816,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C58" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D58" s="16" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E58" s="47">
-        <v>45699</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43790,13 +43833,13 @@
         <v>55</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C59" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D59" s="16" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E59" s="47">
         <v>45699</v>
@@ -43807,16 +43850,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C60" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D60" s="16" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E60" s="47">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43824,16 +43867,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C61" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D61" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E61" s="47">
-        <v>45656</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43841,13 +43884,13 @@
         <v>58</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>722</v>
-      </c>
-      <c r="C62" s="16">
-        <v>2024</v>
-      </c>
-      <c r="D62" s="17" t="s">
-        <v>346</v>
+        <v>723</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>345</v>
       </c>
       <c r="E62" s="47">
         <v>45656</v>
@@ -43858,16 +43901,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>721</v>
-      </c>
-      <c r="C63" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>347</v>
+        <v>722</v>
+      </c>
+      <c r="C63" s="16">
+        <v>2024</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>346</v>
       </c>
       <c r="E63" s="47">
-        <v>45646</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43875,16 +43918,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E64" s="47">
-        <v>45632</v>
+        <v>45646</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43892,16 +43935,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C65" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D65" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E65" s="47">
-        <v>45610</v>
+        <v>45632</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43909,16 +43952,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C66" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D66" s="16" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E66" s="47">
-        <v>45582</v>
+        <v>45610</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43926,16 +43969,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C67" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D67" s="16" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E67" s="47">
-        <v>45572</v>
+        <v>45582</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43943,16 +43986,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C68" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E68" s="47">
-        <v>45569</v>
+        <v>45572</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43960,16 +44003,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C69" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D69" s="16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E69" s="47">
-        <v>45565</v>
+        <v>45569</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43977,16 +44020,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E70" s="47">
-        <v>45552</v>
+        <v>45565</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -43994,16 +44037,16 @@
         <v>67</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C71" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E71" s="47">
-        <v>45535</v>
+        <v>45552</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44011,16 +44054,16 @@
         <v>68</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C72" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D72" s="16" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E72" s="47">
-        <v>45533</v>
+        <v>45535</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44028,16 +44071,16 @@
         <v>69</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C73" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E73" s="47">
-        <v>45526</v>
+        <v>45533</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44045,16 +44088,16 @@
         <v>70</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E74" s="47">
-        <v>45520</v>
+        <v>45526</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44062,16 +44105,16 @@
         <v>71</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C75" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D75" s="16" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E75" s="47">
-        <v>45518</v>
+        <v>45520</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44079,16 +44122,16 @@
         <v>72</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C76" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E76" s="47">
-        <v>45506</v>
+        <v>45518</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44096,16 +44139,16 @@
         <v>73</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C77" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E77" s="47">
-        <v>45498</v>
+        <v>45506</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44113,16 +44156,16 @@
         <v>74</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C78" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D78" s="16" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E78" s="47">
-        <v>45496</v>
+        <v>45498</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44130,16 +44173,16 @@
         <v>75</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C79" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D79" s="16" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E79" s="47">
-        <v>45483</v>
+        <v>45496</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44147,16 +44190,16 @@
         <v>76</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E80" s="47">
-        <v>45471</v>
+        <v>45483</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44164,16 +44207,16 @@
         <v>77</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C81" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D81" s="16" t="s">
-        <v>187</v>
+        <v>364</v>
       </c>
       <c r="E81" s="47">
-        <v>45461</v>
+        <v>45471</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44181,33 +44224,33 @@
         <v>78</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D82" s="16" t="s">
-        <v>365</v>
+        <v>187</v>
       </c>
       <c r="E82" s="47">
-        <v>45455</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
         <v>79</v>
       </c>
-      <c r="B83" s="23" t="s">
-        <v>701</v>
+      <c r="B83" s="17" t="s">
+        <v>702</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D83" s="16" t="s">
-        <v>214</v>
+        <v>365</v>
       </c>
       <c r="E83" s="47">
-        <v>45440</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44215,33 +44258,33 @@
         <v>80</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C84" s="16" t="s">
         <v>112</v>
       </c>
       <c r="D84" s="16" t="s">
-        <v>366</v>
+        <v>214</v>
       </c>
       <c r="E84" s="47">
-        <v>45422</v>
+        <v>45440</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19">
         <v>81</v>
       </c>
-      <c r="B85" s="17" t="s">
-        <v>699</v>
+      <c r="B85" s="23" t="s">
+        <v>700</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D85" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E85" s="47">
-        <v>45400</v>
+        <v>45422</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44249,16 +44292,16 @@
         <v>82</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D86" s="16" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E86" s="47">
-        <v>45384</v>
+        <v>45400</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44266,16 +44309,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>235</v>
+        <v>112</v>
       </c>
       <c r="D87" s="16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E87" s="47">
-        <v>45371</v>
+        <v>45384</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44283,16 +44326,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D88" s="16" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E88" s="47">
-        <v>45369</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -44300,32 +44343,49 @@
         <v>85</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C89" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D89" s="16" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E89" s="47">
-        <v>45338</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>45369</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19">
         <v>86</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C90" s="16" t="s">
         <v>236</v>
       </c>
       <c r="D90" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="E90" s="47">
+        <v>45338</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="19">
+        <v>87</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="D91" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="E90" s="47">
+      <c r="E91" s="47">
         <v>45335</v>
       </c>
     </row>
